--- a/doc/Verification/mini_router_vplan.xlsx
+++ b/doc/Verification/mini_router_vplan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RTL_MINI_PROJECT\mini-router\doc\Verification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D714D01-30C9-4DF4-98E2-99B18941FE8D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611BC9E7-62CC-4A0D-A8A1-B4AFD5F4143E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,9 +72,6 @@
   </si>
   <si>
     <t>Backpressure</t>
-  </si>
-  <si>
-    <t>s_tready = ~fifo_full</t>
   </si>
   <si>
     <t>Stall hold logic</t>
@@ -307,6 +304,11 @@
   <si>
     <t>TC_FUNC_009
 Reset Behaviro Verification</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>s_tready = ~fifo_full verified by SVA. 
+Data integrity verified by scoreboard.</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -894,10 +896,10 @@
         <v>11</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>12</v>
@@ -921,10 +923,10 @@
         <v>11</v>
       </c>
       <c r="C5" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>46</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>47</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>12</v>
@@ -940,7 +942,7 @@
       </c>
       <c r="I5" s="7"/>
     </row>
-    <row r="6" spans="1:9" ht="51" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="63.75" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>10</v>
       </c>
@@ -948,10 +950,10 @@
         <v>16</v>
       </c>
       <c r="C6" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>51</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>52</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>12</v>
@@ -965,8 +967,8 @@
       <c r="H6" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="7" t="s">
-        <v>17</v>
+      <c r="I6" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="63.75" x14ac:dyDescent="0.3">
@@ -977,10 +979,10 @@
         <v>16</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>12</v>
@@ -995,7 +997,7 @@
         <v>15</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
@@ -1003,16 +1005,16 @@
         <v>10</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>13</v>
@@ -1030,16 +1032,16 @@
         <v>10</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>13</v>
@@ -1057,13 +1059,13 @@
         <v>10</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>12</v>
@@ -1078,7 +1080,7 @@
         <v>15</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
@@ -1086,19 +1088,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>12</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>14</v>
@@ -1107,7 +1109,7 @@
         <v>15</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
@@ -1115,13 +1117,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>12</v>
@@ -1139,54 +1141,54 @@
     </row>
     <row r="13" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="C13" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="D13" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>27</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>12</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>15</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="11" t="s">
-        <v>25</v>
-      </c>
       <c r="C14" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="11" t="s">
-        <v>31</v>
-      </c>
       <c r="E14" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>15</v>
@@ -1195,54 +1197,54 @@
     </row>
     <row r="15" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="D15" s="11" t="s">
         <v>33</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>34</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>12</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>15</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>37</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>38</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>12</v>
       </c>
       <c r="F16" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="11" t="s">
         <v>39</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>40</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>15</v>
@@ -1271,7 +1273,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -1282,13 +1284,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1307,7 +1309,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -1321,7 +1323,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5" s="4">
         <f>B3+B4</f>

--- a/doc/Verification/mini_router_vplan.xlsx
+++ b/doc/Verification/mini_router_vplan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RTL_MINI_PROJECT\mini-router\doc\Verification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611BC9E7-62CC-4A0D-A8A1-B4AFD5F4143E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{049437FD-41B1-4EEB-9439-49CD1E88914D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="66">
   <si>
     <t>mini_router Verification Plan</t>
   </si>
@@ -309,6 +309,20 @@
   <si>
     <t>s_tready = ~fifo_full verified by SVA. 
 Data integrity verified by scoreboard.</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Directed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + SVA</t>
+    </r>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -955,8 +969,8 @@
       <c r="D6" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>12</v>
+      <c r="E6" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>13</v>
